--- a/data/matches/leagues/Argentina_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2026.xlsx
@@ -54885,10 +54885,10 @@
         <v>9</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -54897,13 +54897,13 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R119" t="n">
         <v>5</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T119" t="n">
         <v>6</v>
@@ -54937,10 +54937,10 @@
         </is>
       </c>
       <c r="AC119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE119" t="n">
         <v>2.8</v>
@@ -55027,28 +55027,28 @@
         <v>-1</v>
       </c>
       <c r="BG119" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH119" t="n">
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BJ119" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BK119" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BL119" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BM119" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BN119" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BO119" t="n">
         <v>1</v>
@@ -55057,16 +55057,16 @@
         <v>1</v>
       </c>
       <c r="BQ119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS119" t="n">
         <v>2</v>
       </c>
       <c r="BT119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
@@ -55084,13 +55084,13 @@
         <v>87</v>
       </c>
       <c r="BZ119" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="CA119" t="n">
         <v>1.27</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -55123,10 +55123,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN119" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>

--- a/data/matches/leagues/Argentina_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2026.xlsx
@@ -67735,10 +67735,10 @@
         <v>5</v>
       </c>
       <c r="W147" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y147" t="n">
         <v>63</v>

--- a/data/matches/leagues/Argentina_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Argentina_Primera_División_2026.xlsx
@@ -82230,13 +82230,13 @@
         <v>4</v>
       </c>
       <c r="T179" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U179" t="n">
         <v>6</v>
       </c>
       <c r="V179" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W179" t="n">
         <v>16</v>
@@ -82403,10 +82403,10 @@
         <v>0.84</v>
       </c>
       <c r="CA179" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="CB179" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="CC179" t="n">
         <v>0</v>
